--- a/sample.xlsx
+++ b/sample.xlsx
@@ -53,27 +53,27 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>tvg-id</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>tvg-name</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>group-title</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>resolution</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>tvg-logo</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>resolution</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>group-title</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>tvg-name</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>tvg-id</t>
         </is>
       </c>
     </row>
@@ -88,32 +88,32 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>233.18.204.169:5140</t>
+          <t>rtp://233.18.204.169:5140</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t/>
+          <t>300</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>百事通4K (电影)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>影视;高清;4K</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>3840x2160</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>影视;高清;4K</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>百事通4K (电影)</t>
-        </is>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>#&lt;MISSING&gt;</t>
         </is>
       </c>
     </row>
@@ -128,32 +128,32 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>233.18.204.170:5140</t>
+          <t>rtp://233.18.204.170:5140</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t/>
+          <t>301</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>百事通4K (动物)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>影视;高清;4K</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>3840x2160</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>影视;高清;4K</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>百事通4K (动物)</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>#&lt;MISSING&gt;</t>
         </is>
       </c>
     </row>
@@ -168,32 +168,32 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>233.18.204.171:5140</t>
+          <t>rtp://233.18.204.171:5140</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t/>
+          <t>302</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>百事通4K (卡通)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>卡通;高清;4K</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>3840x2160</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>卡通;高清;4K</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>百事通4K (卡通)</t>
-        </is>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>#&lt;MISSING&gt;</t>
         </is>
       </c>
     </row>
@@ -208,32 +208,32 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>233.18.204.174:5140</t>
+          <t>rtp://233.18.204.174:5140</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>CHC动作电影</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>影视;高清</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1920x1080</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>https://epg.deny.vip/szpd/CHC3.png</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>1920x1080</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>影视;高清</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>CHC动作电影</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>200</t>
         </is>
       </c>
     </row>
@@ -248,32 +248,32 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>233.18.204.173:5140</t>
+          <t>rtp://233.18.204.173:5140</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>CHC家庭影院</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>影视;高清</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1920x1080</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>https://epg.deny.vip/szpd/CHC2.png</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>1920x1080</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>影视;高清</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>CHC家庭影院</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>201</t>
         </is>
       </c>
     </row>
@@ -288,32 +288,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>233.18.204.175:5140</t>
+          <t>rtp://233.18.204.175:5140</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>CHC影迷电影</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>影视;高清</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1920x1080</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>https://epg.deny.vip/szpd/CHC1.png</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>1920x1080</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>影视;高清</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>CHC影迷电影</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>202</t>
         </is>
       </c>
     </row>
@@ -328,32 +328,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>233.18.204.57:5140</t>
+          <t>rtp://233.18.204.57:5140</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>新闻综合</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>地方;高清</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1920x1080</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>https://epg.deny.vip/df/新闻综合.png</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>1920x1080</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>地方;高清</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>新闻综合</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>203</t>
         </is>
       </c>
     </row>
@@ -368,32 +368,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>233.18.204.51:5140</t>
+          <t>rtp://233.18.204.51:5140</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>东方卫视</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>地方;高清</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1920x1080</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>https://epg.deny.vip/ws/dongfang.png</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>1920x1080</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>地方;高清</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>东方卫视</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>204</t>
         </is>
       </c>
     </row>
@@ -408,32 +408,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>233.18.204.55:5140</t>
+          <t>rtp://233.18.204.55:5140</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>东方影视</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>地方;影视;高清</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1920x1080</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>https://epg.deny.vip/df/东方影视.png</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>1920x1080</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>地方;影视;高清</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>东方影视</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>205</t>
         </is>
       </c>
     </row>
@@ -448,32 +448,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>233.18.204.58:5140</t>
+          <t>rtp://233.18.204.58:5140</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>五星体育</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>地方;体育;高清</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1920x1080</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>https://epg.deny.vip/df/五星体育.png</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>1920x1080</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>地方;体育;高清</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>五星体育</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>206</t>
         </is>
       </c>
     </row>
@@ -488,32 +488,32 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>233.18.204.47:5140</t>
+          <t>rtp://233.18.204.47:5140</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>乐游</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>地方;高清</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1920x1080</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>https://epg.deny.vip/df/乐游.png</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>1920x1080</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>地方;高清</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>乐游</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>207</t>
         </is>
       </c>
     </row>
@@ -528,32 +528,32 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>233.18.204.63:5140</t>
+          <t>rtp://233.18.204.63:5140</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>上海教育</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>地方;高清</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1920x1080</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>https://epg.deny.vip/df/上海教育.png</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>1920x1080</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>地方;高清</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>上海教育</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>208</t>
         </is>
       </c>
     </row>
@@ -568,32 +568,32 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>233.18.204.45:5140</t>
+          <t>rtp://233.18.204.45:5140</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>生活时尚</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>地方;高清</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1920x1080</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>https://epg.deny.vip/df/生活时尚.png</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>1920x1080</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>地方;高清</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>生活时尚</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>209</t>
         </is>
       </c>
     </row>
@@ -608,32 +608,32 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>233.18.204.54:5140</t>
+          <t>rtp://233.18.204.54:5140</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>哈哈炫动</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>地方;卡通;高清</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1920x1080</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
           <t>https://epg.deny.vip/df/哈哈炫动.png</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>1920x1080</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>地方;卡通;高清</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>哈哈炫动</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>210</t>
         </is>
       </c>
     </row>
@@ -648,32 +648,32 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>233.18.204.46:5140</t>
+          <t>rtp://233.18.204.46:5140</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>动漫秀场</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>地方;卡通;高清</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1920x1080</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>https://epg.deny.vip/df/动漫秀场.png</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>1920x1080</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>地方;卡通;高清</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>动漫秀场</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>211</t>
         </is>
       </c>
     </row>
@@ -688,32 +688,32 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>233.18.204.48:5140</t>
+          <t>rtp://233.18.204.48:5140</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>都市剧场</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>地方;高清</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1920x1080</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
           <t>https://epg.deny.vip/df/都市剧场.png</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>1920x1080</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>地方;高清</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>都市剧场</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>212</t>
         </is>
       </c>
     </row>
@@ -728,32 +728,32 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>233.18.204.53:5140</t>
+          <t>rtp://233.18.204.53:5140</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>都市频道</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>地方;高清</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1920x1080</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
           <t>https://epg.deny.vip/df/都市频道.png</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>1920x1080</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>地方;高清</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>都市频道</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>213</t>
         </is>
       </c>
     </row>
@@ -768,32 +768,32 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>233.18.204.66:5140</t>
+          <t>rtp://233.18.204.66:5140</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>金色学堂</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>地方;高清</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1920x1080</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
           <t>https://epg.deny.vip/df/金色学堂.png</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>1920x1080</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>地方;高清</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>金色学堂</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>214</t>
         </is>
       </c>
     </row>
@@ -808,32 +808,32 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>233.18.204.49:5140</t>
+          <t>rtp://233.18.204.49:5140</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>法治天地</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>地方;高清</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1920x1080</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
           <t>https://epg.deny.vip/df/法治天地.png</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>1920x1080</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>地方;高清</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>法治天地</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>215</t>
         </is>
       </c>
     </row>
@@ -848,32 +848,32 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>233.18.204.59:5140</t>
+          <t>rtp://233.18.204.59:5140</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>第一财经</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>地方;高清</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1920x1080</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
           <t>https://epg.deny.vip/df/第一财经.png</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>1920x1080</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>地方;高清</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>第一财经</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>216</t>
         </is>
       </c>
     </row>
@@ -888,32 +888,32 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>233.18.204.65:5140</t>
+          <t>rtp://233.18.204.65:5140</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>东方财经</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>地方;高清</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1920x1080</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
           <t>https://epg.deny.vip/df/东方财经.png</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>1920x1080</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>地方;高清</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>东方财经</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>217</t>
         </is>
       </c>
     </row>
@@ -928,32 +928,32 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>233.18.204.44:5140</t>
+          <t>rtp://233.18.204.44:5140</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>游戏风云</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>地方;高清</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1920x1080</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
           <t>https://epg.deny.vip/df/游戏风云.png</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>1920x1080</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>地方;高清</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>游戏风云</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>218</t>
         </is>
       </c>
     </row>
@@ -963,37 +963,37 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>CCTV-1HD</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>rtp://233.18.204.52:5140</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>CCTV-1</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>233.18.204.168:5140</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>央视;高清</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1920x1080</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
         <is>
           <t>https://epg.deny.vip/cctv/CCTV-1.png</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>1920x1080</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>央视;高清</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>CCTV-1</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>219</t>
         </is>
       </c>
     </row>
@@ -1003,22 +1003,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CCTV-1HD</t>
+          <t>CCTV-2HD</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>233.18.204.52:5140</t>
+          <t>rtp://233.18.204.68:5140</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/cctv/CCTV-1.png</t>
+          <t>221</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>CCTV-2</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>CCTV-1</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>https://epg.deny.vip/cctv/CCTV-2.png</t>
         </is>
       </c>
     </row>
@@ -1043,22 +1043,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CCTV-2HD</t>
+          <t>CCTV-3HD</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>233.18.204.68:5140</t>
+          <t>rtp://233.18.204.69:5140</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/cctv/CCTV-2.png</t>
+          <t>222</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>CCTV-3</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1068,12 +1068,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>CCTV-2</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>https://epg.deny.vip/cctv/CCTV-3.png</t>
         </is>
       </c>
     </row>
@@ -1083,22 +1083,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CCTV-3HD</t>
+          <t>CCTV-4HD</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>233.18.204.69:5140</t>
+          <t>rtp://233.18.204.70:5140</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/cctv/CCTV-3.png</t>
+          <t>223</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>CCTV-4</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>CCTV-3</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>https://epg.deny.vip/cctv/CCTV-4.png</t>
         </is>
       </c>
     </row>
@@ -1123,37 +1123,37 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CCTV-4HD</t>
+          <t>CCTV-5+HD</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>233.18.204.70:5140</t>
+          <t>rtp://233.18.204.67:5140</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/cctv/CCTV-4.png</t>
+          <t>224</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>CCTV-5+</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>央视;高清</t>
+          <t>央视;体育;高清</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>CCTV-4</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>https://epg.deny.vip/cctv/CCTV-5+.png</t>
         </is>
       </c>
     </row>
@@ -1163,22 +1163,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CCTV-5+HD</t>
+          <t>CCTV-5HD</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>233.18.204.67:5140</t>
+          <t>rtp://233.18.204.71:5140</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/cctv/CCTV-5+.png</t>
+          <t>225</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>CCTV-5</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1188,12 +1188,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>CCTV-5+</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>https://epg.deny.vip/cctv/CCTV-5.png</t>
         </is>
       </c>
     </row>
@@ -1203,37 +1203,37 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CCTV-5HD</t>
+          <t>CCTV-6HD</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>233.18.204.71:5140</t>
+          <t>rtp://233.18.204.72:5140</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/cctv/CCTV-5.png</t>
+          <t>226</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>CCTV-6</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>央视;体育;高清</t>
+          <t>央视;影视;高清</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>CCTV-5</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>https://epg.deny.vip/cctv/CCTV-6.png</t>
         </is>
       </c>
     </row>
@@ -1243,37 +1243,37 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CCTV-6HD</t>
+          <t>CCTV-7HD</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>233.18.204.72:5140</t>
+          <t>rtp://233.18.204.73:5140</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/cctv/CCTV-6.png</t>
+          <t>227</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>CCTV-7</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>央视;影视;高清</t>
+          <t>央视;高清</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>CCTV-6</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>https://epg.deny.vip/cctv/CCTV-7.png</t>
         </is>
       </c>
     </row>
@@ -1283,22 +1283,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CCTV-7HD</t>
+          <t>CCTV-8HD</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>233.18.204.73:5140</t>
+          <t>rtp://233.18.204.74:5140</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/cctv/CCTV-7.png</t>
+          <t>228</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>CCTV-8</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>CCTV-7</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>https://epg.deny.vip/cctv/CCTV-8.png</t>
         </is>
       </c>
     </row>
@@ -1323,22 +1323,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CCTV-8HD</t>
+          <t>CCTV-9HD</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>233.18.204.74:5140</t>
+          <t>rtp://233.18.204.75:5140</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/cctv/CCTV-8.png</t>
+          <t>229</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>CCTV-9</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>CCTV-8</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>https://epg.deny.vip/cctv/CCTV-9.png</t>
         </is>
       </c>
     </row>
@@ -1363,22 +1363,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CCTV-9HD</t>
+          <t>CCTV-10HD</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>233.18.204.75:5140</t>
+          <t>rtp://233.18.204.76:5140</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/cctv/CCTV-9.png</t>
+          <t>230</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>CCTV-10</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1388,12 +1388,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>CCTV-9</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>https://epg.deny.vip/cctv/CCTV-10.png</t>
         </is>
       </c>
     </row>
@@ -1403,22 +1403,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CCTV-10HD</t>
+          <t>CCTV-11HD</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>233.18.204.76:5140</t>
+          <t>rtp://233.18.204.77:5140</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/cctv/CCTV-10.png</t>
+          <t>231</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>CCTV-11</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>CCTV-10</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>https://epg.deny.vip/cctv/CCTV-11.png</t>
         </is>
       </c>
     </row>
@@ -1443,22 +1443,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CCTV-11HD</t>
+          <t>CCTV-12HD</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>233.18.204.77:5140</t>
+          <t>rtp://233.18.204.78:5140</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/cctv/CCTV-11.png</t>
+          <t>232</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>CCTV-12</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>CCTV-11</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>https://epg.deny.vip/cctv/CCTV-12.png</t>
         </is>
       </c>
     </row>
@@ -1483,22 +1483,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CCTV-12HD</t>
+          <t>CCTV-13HD</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>233.18.204.78:5140</t>
+          <t>rtp://233.18.204.79:5140</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/cctv/CCTV-12.png</t>
+          <t>233</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>CCTV-13</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1508,12 +1508,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>CCTV-12</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>https://epg.deny.vip/cctv/CCTV-13.png</t>
         </is>
       </c>
     </row>
@@ -1523,22 +1523,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CCTV-13HD</t>
+          <t>CCTV-14HD</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>233.18.204.79:5140</t>
+          <t>rtp://233.18.204.80:5140</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/cctv/CCTV-13.png</t>
+          <t>234</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>CCTV-14</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1548,12 +1548,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>CCTV-13</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>https://epg.deny.vip/cctv/CCTV-14.png</t>
         </is>
       </c>
     </row>
@@ -1563,22 +1563,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CCTV-14HD</t>
+          <t>CCTV-15HD</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>233.18.204.80:5140</t>
+          <t>rtp://233.18.204.81:5140</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/cctv/CCTV-14.png</t>
+          <t>235</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>CCTV-15</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1588,12 +1588,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>CCTV-14</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>https://epg.deny.vip/cctv/CCTV-15.png</t>
         </is>
       </c>
     </row>
@@ -1603,37 +1603,37 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CCTV-15HD</t>
+          <t>CCTV-16HD</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>233.18.204.81:5140</t>
+          <t>rtp://233.18.204.82:5140</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/cctv/CCTV-15.png</t>
+          <t>236</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>CCTV-16</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>央视;高清</t>
+          <t>央视;体育;高清</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>CCTV-15</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>https://epg.deny.vip/cctv/CCTV-16.png</t>
         </is>
       </c>
     </row>
@@ -1643,37 +1643,37 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CCTV-16HD</t>
+          <t>CCTV-17HD</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>233.18.204.82:5140</t>
+          <t>rtp://233.18.204.83:5140</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/cctv/CCTV-16.png</t>
+          <t>237</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>CCTV-17</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>央视;体育;高清</t>
+          <t>央视;高清</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>CCTV-16</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>https://epg.deny.vip/cctv/CCTV-17.png</t>
         </is>
       </c>
     </row>
@@ -1683,22 +1683,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CCTV-17HD</t>
+          <t>央视文化精品HD</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>233.18.204.83:5140</t>
+          <t>rtp://233.18.204.186:5140</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/cctv/CCTV-17.png</t>
+          <t>238</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>央视文化精品</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>CCTV-17</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>https://epg.deny.vip/cctv/CCTV-YSWHJP.png</t>
         </is>
       </c>
     </row>
@@ -1723,37 +1723,37 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>央视文化精品HD</t>
+          <t>第一剧场HD</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>233.18.204.186:5140</t>
+          <t>rtp://233.18.204.184:5140</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/cctv/CCTV-YSWHJP.png</t>
+          <t>239</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>第一剧场</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>央视;高清</t>
+          <t>央视;影视;高清</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>央视文化精品</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>https://epg.deny.vip/cctv/CCTV-DYJC.png</t>
         </is>
       </c>
     </row>
@@ -1763,37 +1763,37 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>第一剧场HD</t>
+          <t>怀旧剧场HD</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>233.18.204.184:5140</t>
+          <t>rtp://233.18.204.182:5140</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/cctv/CCTV-DYJC.png</t>
+          <t>240</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>怀旧剧场</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>央视;影视;高清</t>
+          <t>央视;高清</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>第一剧场</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>https://epg.deny.vip/cctv/CCTV-HJJC.png</t>
         </is>
       </c>
     </row>
@@ -1803,22 +1803,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>怀旧剧场HD</t>
+          <t>兵器科技HD</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>233.18.204.182:5140</t>
+          <t>rtp://233.18.204.178:5140</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/cctv/CCTV-HJJC.png</t>
+          <t>241</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>兵器科技</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>怀旧剧场</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>https://epg.deny.vip/cctv/CCTV-BQKJ.png</t>
         </is>
       </c>
     </row>
@@ -1843,37 +1843,37 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>兵器科技HD</t>
+          <t>风云剧场HD</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>233.18.204.178:5140</t>
+          <t>rtp://233.18.204.183:5140</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/cctv/CCTV-BQKJ.png</t>
+          <t>242</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>风云剧场</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>央视;高清</t>
+          <t>央视;影视;高清</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>兵器科技</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>https://epg.deny.vip/cctv/CCTV-FYJC.png</t>
         </is>
       </c>
     </row>
@@ -1883,37 +1883,37 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>风云剧场HD</t>
+          <t>风云音乐HD</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>233.18.204.183:5140</t>
+          <t>rtp://233.18.204.185:5140</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/cctv/CCTV-FYJC.png</t>
+          <t>243</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>风云音乐</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>央视;影视;高清</t>
+          <t>央视;高清</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>风云剧场</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>https://epg.deny.vip/cctv/CCTV-FYYY.png</t>
         </is>
       </c>
     </row>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>风云音乐HD</t>
+          <t>高尔夫网球HD</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>233.18.204.185:5140</t>
+          <t>rtp://233.18.204.181:5140</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/cctv/CCTV-FYYY.png</t>
+          <t>244</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>高尔夫网球</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1948,12 +1948,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>风云音乐</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>https://epg.deny.vip/cctv/CCTV-GEFWQ.png</t>
         </is>
       </c>
     </row>
@@ -1963,22 +1963,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>高尔夫网球HD</t>
+          <t>女性时尚HD</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>233.18.204.181:5140</t>
+          <t>rtp://233.18.204.180:5140</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/cctv/CCTV-GEFWQ.png</t>
+          <t>245</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>女性时尚</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -1988,12 +1988,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>高尔夫网球</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>https://epg.deny.vip/cctv/CCTV-NXSS.png</t>
         </is>
       </c>
     </row>
@@ -2003,22 +2003,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>女性时尚HD</t>
+          <t>世界地理HD</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>233.18.204.180:5140</t>
+          <t>rtp://233.18.204.179:5140</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/cctv/CCTV-NXSS.png</t>
+          <t>246</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>世界地理</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2028,12 +2028,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>女性时尚</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>https://epg.deny.vip/cctv/CCTV-SJDL.png</t>
         </is>
       </c>
     </row>
@@ -2043,22 +2043,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>世界地理HD</t>
+          <t>早期教育HD</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>233.18.204.179:5140</t>
+          <t>rtp://233.18.204.187:5140</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/cctv/CCTV-SJDL.png</t>
+          <t>247</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>早期教育</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>世界地理</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>https://epg.deny.vip/szpd/CETV-ZQJY.png</t>
         </is>
       </c>
     </row>
@@ -2083,37 +2083,37 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>早期教育HD</t>
+          <t>CETV-1HD</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>233.18.204.187:5140</t>
+          <t>rtp://233.18.204.98:5140</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/szpd/CETV-ZQJY.png</t>
+          <t>248</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>CETV-1</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>央视;高清</t>
+          <t>卫视;高清</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>早期教育</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>https://epg.deny.vip/cctv/CETV-1.png</t>
         </is>
       </c>
     </row>
@@ -2123,22 +2123,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CETV-1HD</t>
+          <t>CETV-4HD</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>233.18.204.98:5140</t>
+          <t>rtp://233.18.204.111:5140</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/cctv/CETV-1.png</t>
+          <t>249</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>CETV-4</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>CETV-1</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>https://epg.deny.vip/cctv/CETV-4.png</t>
         </is>
       </c>
     </row>
@@ -2163,22 +2163,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CETV-4HD</t>
+          <t>安徽卫视HD</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>233.18.204.111:5140</t>
+          <t>rtp://233.18.204.93:5140</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/cctv/CETV-4.png</t>
+          <t>250</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>安徽卫视</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>CETV-4</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>https://epg.deny.vip/ws/anhui.png</t>
         </is>
       </c>
     </row>
@@ -2203,22 +2203,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>安徽卫视HD</t>
+          <t>北京卫视HD</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>233.18.204.93:5140</t>
+          <t>rtp://233.18.204.87:5140</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/anhui.png</t>
+          <t>251</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>北京卫视</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>安徽卫视</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>https://epg.deny.vip/ws/beijing.png</t>
         </is>
       </c>
     </row>
@@ -2243,22 +2243,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>北京卫视HD</t>
+          <t>兵团卫视HD</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>233.18.204.87:5140</t>
+          <t>rtp://233.18.204.221:5140</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/beijing.png</t>
+          <t>252</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>兵团卫视</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>北京卫视</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>https://epg.deny.vip/ws/bingtuan.png</t>
         </is>
       </c>
     </row>
@@ -2283,22 +2283,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>兵团卫视HD</t>
+          <t>茶频道HD</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>233.18.204.221:5140</t>
+          <t>rtp://233.18.204.43:5140</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/bingtuan.png</t>
+          <t>253</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>茶频道</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>兵团卫视</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>https://epg.deny.vip/df/茶频道.png</t>
         </is>
       </c>
     </row>
@@ -2323,22 +2323,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>茶频道HD</t>
+          <t>东南卫视HD</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>233.18.204.43:5140</t>
+          <t>rtp://233.18.204.94:5140</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/df/茶频道.png</t>
+          <t>254</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>东南卫视</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2348,12 +2348,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>茶频道</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>https://epg.deny.vip/ws/dongnan.png</t>
         </is>
       </c>
     </row>
@@ -2363,22 +2363,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>东南卫视HD</t>
+          <t>甘肃卫视HD</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>233.18.204.94:5140</t>
+          <t>rtp://233.18.204.110:5140</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/dongnan.png</t>
+          <t>255</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>甘肃卫视</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>东南卫视</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>https://epg.deny.vip/ws/gansu.png</t>
         </is>
       </c>
     </row>
@@ -2403,22 +2403,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>甘肃卫视HD</t>
+          <t>广东卫视HD</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>233.18.204.110:5140</t>
+          <t>rtp://233.18.204.88:5140</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/gansu.png</t>
+          <t>256</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>广东卫视</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2428,12 +2428,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>甘肃卫视</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>https://epg.deny.vip/ws/guangdong.png</t>
         </is>
       </c>
     </row>
@@ -2443,22 +2443,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>广东卫视HD</t>
+          <t>广西卫视HD</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>233.18.204.88:5140</t>
+          <t>rtp://233.18.204.107:5140</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/guangdong.png</t>
+          <t>257</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>广西卫视</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>广东卫视</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>https://epg.deny.vip/ws/guangxi.png</t>
         </is>
       </c>
     </row>
@@ -2483,22 +2483,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>广西卫视HD</t>
+          <t>贵州卫视HD</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>233.18.204.107:5140</t>
+          <t>rtp://233.18.204.101:5140</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/guangxi.png</t>
+          <t>258</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>贵州卫视</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2508,12 +2508,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>广西卫视</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>https://epg.deny.vip/ws/guizhou.png</t>
         </is>
       </c>
     </row>
@@ -2523,22 +2523,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>贵州卫视HD</t>
+          <t>海南卫视HD</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>233.18.204.101:5140</t>
+          <t>rtp://233.18.204.102:5140</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/guizhou.png</t>
+          <t>259</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>海南卫视</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2548,12 +2548,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>贵州卫视</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>https://epg.deny.vip/ws/hainan.png</t>
         </is>
       </c>
     </row>
@@ -2563,22 +2563,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>海南卫视HD</t>
+          <t>河北卫视HD</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>233.18.204.102:5140</t>
+          <t>rtp://233.18.204.103:5140</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/hainan.png</t>
+          <t>260</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>河北卫视</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>海南卫视</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>https://epg.deny.vip/ws/hebei.png</t>
         </is>
       </c>
     </row>
@@ -2603,22 +2603,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>河北卫视HD</t>
+          <t>河南卫视HD</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>233.18.204.103:5140</t>
+          <t>rtp://233.18.204.105:5140</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/hebei.png</t>
+          <t>261</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>河南卫视</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>河北卫视</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>https://epg.deny.vip/ws/henan.png</t>
         </is>
       </c>
     </row>
@@ -2643,22 +2643,22 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>河南卫视HD</t>
+          <t>黑龙江卫视HD</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>233.18.204.105:5140</t>
+          <t>rtp://233.18.204.90:5140</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/henan.png</t>
+          <t>262</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>黑龙江卫视</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2668,12 +2668,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>河南卫视</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>https://epg.deny.vip/ws/heilongjiang.png</t>
         </is>
       </c>
     </row>
@@ -2683,22 +2683,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>黑龙江卫视HD</t>
+          <t>湖北卫视HD</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>233.18.204.90:5140</t>
+          <t>rtp://233.18.204.92:5140</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/heilongjiang.png</t>
+          <t>263</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>湖北卫视</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2708,12 +2708,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>黑龙江卫视</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>https://epg.deny.vip/ws/hubei.png</t>
         </is>
       </c>
     </row>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>湖北卫视HD</t>
+          <t>湖南卫视HD</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>233.18.204.92:5140</t>
+          <t>rtp://233.18.204.86:5140</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/hubei.png</t>
+          <t>264</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>湖南卫视</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>湖北卫视</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>https://epg.deny.vip/ws/hunan.png</t>
         </is>
       </c>
     </row>
@@ -2763,22 +2763,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>湖南卫视HD</t>
+          <t>吉林卫视HD</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>233.18.204.86:5140</t>
+          <t>rtp://233.18.204.108:5140</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/hunan.png</t>
+          <t>265</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>吉林卫视</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2788,12 +2788,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>湖南卫视</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>https://epg.deny.vip/ws/jilin.png</t>
         </is>
       </c>
     </row>
@@ -2803,22 +2803,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>吉林卫视HD</t>
+          <t>江苏卫视HD</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>233.18.204.108:5140</t>
+          <t>rtp://233.18.204.85:5140</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/jilin.png</t>
+          <t>266</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>江苏卫视</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>吉林卫视</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>https://epg.deny.vip/ws/jiangsu.png</t>
         </is>
       </c>
     </row>
@@ -2843,22 +2843,22 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>江苏卫视HD</t>
+          <t>江西卫视HD</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>233.18.204.85:5140</t>
+          <t>rtp://233.18.204.95:5140</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/jiangsu.png</t>
+          <t>267</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>江西卫视</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>江苏卫视</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>https://epg.deny.vip/ws/jiangxi.png</t>
         </is>
       </c>
     </row>
@@ -2883,22 +2883,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>江西卫视HD</t>
+          <t>云南卫视HD</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>233.18.204.95:5140</t>
+          <t>rtp://233.18.204.106:5140</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/jiangxi.png</t>
+          <t>268</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>云南卫视</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2908,12 +2908,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>江西卫视</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>https://epg.deny.vip/ws/yunnan.png</t>
         </is>
       </c>
     </row>
@@ -2923,22 +2923,22 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>云南卫视HD</t>
+          <t>金鹰纪实HD</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>233.18.204.106:5140</t>
+          <t>rtp://233.18.204.104:5140</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/yunnan.png</t>
+          <t>269</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>金鹰纪实</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2948,12 +2948,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>云南卫视</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>https://epg.deny.vip/df/金鹰纪实.png</t>
         </is>
       </c>
     </row>
@@ -2963,37 +2963,37 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>金鹰纪实HD</t>
+          <t>金鹰卡通HD</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>233.18.204.104:5140</t>
+          <t>rtp://233.18.204.113:5140</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/df/金鹰纪实.png</t>
+          <t>270</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>金鹰卡通</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>卫视;高清</t>
+          <t>卫视;卡通;高清</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>金鹰纪实</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>https://epg.deny.vip/df/金鹰卡通.png</t>
         </is>
       </c>
     </row>
@@ -3003,22 +3003,22 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>金鹰卡通HD</t>
+          <t>卡酷少儿HD</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>233.18.204.113:5140</t>
+          <t>rtp://233.18.204.109:5140</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/df/金鹰卡通.png</t>
+          <t>271</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>卡酷少儿</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>金鹰卡通</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>https://epg.deny.vip/df/卡酷少儿.png</t>
         </is>
       </c>
     </row>
@@ -3043,37 +3043,37 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>卡酷少儿HD</t>
+          <t>快乐垂钓HD</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>233.18.204.109:5140</t>
+          <t>rtp://233.18.204.42:5140</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/df/卡酷少儿.png</t>
+          <t>272</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>快乐垂钓</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>卫视;卡通;高清</t>
+          <t>卫视;高清</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>卡酷少儿</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>https://epg.deny.vip/df/快乐垂钓.png</t>
         </is>
       </c>
     </row>
@@ -3083,22 +3083,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>快乐垂钓HD</t>
+          <t>辽宁卫视HD</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>233.18.204.42:5140</t>
+          <t>rtp://233.18.204.96:5140</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/df/快乐垂钓.png</t>
+          <t>273</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>辽宁卫视</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>快乐垂钓</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>https://epg.deny.vip/ws/liaoning.png</t>
         </is>
       </c>
     </row>
@@ -3123,22 +3123,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>辽宁卫视HD</t>
+          <t>内蒙古卫视HD</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>233.18.204.96:5140</t>
+          <t>rtp://233.18.204.217:5140</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/liaoning.png</t>
+          <t>274</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>内蒙古卫视</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>辽宁卫视</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>https://epg.deny.vip/ws/neimeng.png</t>
         </is>
       </c>
     </row>
@@ -3163,22 +3163,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>内蒙古卫视HD</t>
+          <t>宁夏卫视HD</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>233.18.204.217:5140</t>
+          <t>rtp://233.18.204.230:5140</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/neimeng.png</t>
+          <t>275</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>宁夏卫视</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>内蒙古卫视</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>https://epg.deny.vip/ws/ningxia.png</t>
         </is>
       </c>
     </row>
@@ -3203,22 +3203,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>宁夏卫视HD</t>
+          <t>青海卫视HD</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>233.18.204.230:5140</t>
+          <t>rtp://233.18.204.112:5140</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/ningxia.png</t>
+          <t>276</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>青海卫视</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3228,12 +3228,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>宁夏卫视</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>https://epg.deny.vip/ws/qinghai.png</t>
         </is>
       </c>
     </row>
@@ -3243,22 +3243,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>青海卫视HD</t>
+          <t>三沙卫视HD</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>233.18.204.112:5140</t>
+          <t>rtp://233.18.204.172:5140</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/qinghai.png</t>
+          <t>277</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>三沙卫视</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3268,12 +3268,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>青海卫视</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>https://epg.deny.vip/ws/sansha.png</t>
         </is>
       </c>
     </row>
@@ -3283,22 +3283,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>三沙卫视HD</t>
+          <t>山东卫视HD</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>233.18.204.172:5140</t>
+          <t>rtp://233.18.204.91:5140</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/sansha.png</t>
+          <t>278</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>山东卫视</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>三沙卫视</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>https://epg.deny.vip/ws/shandong.png</t>
         </is>
       </c>
     </row>
@@ -3323,22 +3323,22 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>山东卫视HD</t>
+          <t>山西卫视HD</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>233.18.204.91:5140</t>
+          <t>rtp://233.18.204.211:5140</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/shandong.png</t>
+          <t>279</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>山西卫视</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3348,12 +3348,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>山东卫视</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>https://epg.deny.vip/ws/shanxi_.png</t>
         </is>
       </c>
     </row>
@@ -3363,22 +3363,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>山西卫视HD</t>
+          <t>陕西卫视HD</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>233.18.204.211:5140</t>
+          <t>rtp://233.18.204.223:5140</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/shanxi_.png</t>
+          <t>280</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>陕西卫视</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>山西卫视</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>https://epg.deny.vip/ws/shanxi.png</t>
         </is>
       </c>
     </row>
@@ -3403,22 +3403,22 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>陕西卫视HD</t>
+          <t>深圳卫视HD</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>233.18.204.223:5140</t>
+          <t>rtp://233.18.204.89:5140</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/shanxi.png</t>
+          <t>281</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>深圳卫视</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>陕西卫视</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>https://epg.deny.vip/ws/shenzhen.png</t>
         </is>
       </c>
     </row>
@@ -3443,22 +3443,22 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>深圳卫视HD</t>
+          <t>四川卫视HD</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>233.18.204.89:5140</t>
+          <t>rtp://233.18.204.99:5140</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/shenzhen.png</t>
+          <t>282</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>四川卫视</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3468,12 +3468,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>深圳卫视</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>https://epg.deny.vip/ws/sichuan.png</t>
         </is>
       </c>
     </row>
@@ -3483,22 +3483,22 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>四川卫视HD</t>
+          <t>天津卫视HD</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>233.18.204.99:5140</t>
+          <t>rtp://233.18.204.97:5140</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/sichuan.png</t>
+          <t>283</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>天津卫视</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>四川卫视</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>https://epg.deny.vip/ws/tianjin.png</t>
         </is>
       </c>
     </row>
@@ -3523,22 +3523,22 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>天津卫视HD</t>
+          <t>西藏卫视HD</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>233.18.204.97:5140</t>
+          <t>rtp://233.18.204.222:5140</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/tianjin.png</t>
+          <t>284</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>西藏卫视</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>天津卫视</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>https://epg.deny.vip/ws/xizang.png</t>
         </is>
       </c>
     </row>
@@ -3563,22 +3563,22 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>西藏卫视HD</t>
+          <t>新疆卫视HD</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>233.18.204.222:5140</t>
+          <t>rtp://233.18.204.220:5140</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/xizang.png</t>
+          <t>285</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>新疆卫视</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>西藏卫视</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>https://epg.deny.vip/ws/xinjiang.png</t>
         </is>
       </c>
     </row>
@@ -3603,22 +3603,22 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>新疆卫视HD</t>
+          <t>浙江卫视HD</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>233.18.204.220:5140</t>
+          <t>rtp://233.18.204.84:5140</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/xinjiang.png</t>
+          <t>286</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>浙江卫视</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3628,12 +3628,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>新疆卫视</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>https://epg.deny.vip/ws/zhejiang.png</t>
         </is>
       </c>
     </row>
@@ -3643,22 +3643,22 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>浙江卫视HD</t>
+          <t>重庆卫视 HD</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>233.18.204.84:5140</t>
+          <t>rtp://233.18.204.100:5140</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/zhejiang.png</t>
+          <t>287</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>重庆卫视</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3668,12 +3668,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>浙江卫视</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>https://epg.deny.vip/ws/chongqing.png</t>
         </is>
       </c>
     </row>
@@ -3683,37 +3683,37 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>重庆卫视 HD</t>
+          <t>东方购物-1HD</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>233.18.204.100:5140</t>
+          <t>rtp://233.18.204.61:5140</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/chongqing.png</t>
+          <t>288</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>东方购物-1</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>卫视;高清</t>
+          <t>购物;高清</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>重庆卫视</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>#&lt;MISSING&gt;</t>
         </is>
       </c>
     </row>
@@ -3723,22 +3723,22 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>东方购物-1HD</t>
+          <t>东方购物-2HD</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>233.18.204.61:5140</t>
+          <t>rtp://233.18.204.62:5140</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t/>
+          <t>289</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>东方购物-2</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3748,12 +3748,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>东方购物-1</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>#&lt;MISSING&gt;</t>
         </is>
       </c>
     </row>
@@ -3763,37 +3763,37 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>东方购物-2HD</t>
+          <t>新闻综合</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>233.18.204.62:5140</t>
+          <t>rtp://233.18.204.189:5140</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>新闻综合</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>购物;高清</t>
+          <t>地方;标清</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>东方购物-2</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>https://epg.deny.vip/df/新闻综合.png</t>
         </is>
       </c>
     </row>
@@ -3803,22 +3803,22 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>新闻综合</t>
+          <t>东方卫视</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>233.18.204.189:5140</t>
+          <t>rtp://233.18.204.1:5140</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/df/新闻综合.png</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>东方卫视</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>新闻综合</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>https://epg.deny.vip/ws/dongfang.png</t>
         </is>
       </c>
     </row>
@@ -3843,37 +3843,37 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>东方卫视</t>
+          <t>东方影视</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>233.18.204.1:5140</t>
+          <t>rtp://233.18.204.4:5140</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/dongfang.png</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>东方影视</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>地方;标清</t>
+          <t>地方;标清;影视</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>东方卫视</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>https://epg.deny.vip/df/东方影视.png</t>
         </is>
       </c>
     </row>
@@ -3883,37 +3883,37 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>东方影视</t>
+          <t>五星体育</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>233.18.204.4:5140</t>
+          <t>rtp://233.18.204.6:5140</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/df/东方影视.png</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>五星体育</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>地方;标清;影视</t>
+          <t>地方;体育;标清</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>东方影视</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>https://epg.deny.vip/df/五星体育.png</t>
         </is>
       </c>
     </row>
@@ -3923,37 +3923,37 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>五星体育</t>
+          <t>上海教育</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>233.18.204.6:5140</t>
+          <t>rtp://233.18.204.11:5140</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/df/五星体育.png</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>上海教育</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>地方;体育;标清</t>
+          <t>标清</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>五星体育</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>https://epg.deny.vip/df/上海教育.png</t>
         </is>
       </c>
     </row>
@@ -3963,37 +3963,37 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>上海教育</t>
+          <t>哈哈炫动</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>233.18.204.11:5140</t>
+          <t>rtp://233.18.204.7:5140</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/df/上海教育.png</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>哈哈炫动</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>标清</t>
+          <t>标清;卡通</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>上海教育</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>https://epg.deny.vip/df/哈哈炫动.png</t>
         </is>
       </c>
     </row>
@@ -4003,37 +4003,37 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>哈哈炫动</t>
+          <t>都市频道</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>233.18.204.7:5140</t>
+          <t>rtp://233.18.204.2:5140</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/df/哈哈炫动.png</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>都市频道</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>标清;卡通</t>
+          <t>地方;标清</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>哈哈炫动</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>https://epg.deny.vip/df/都市频道.png</t>
         </is>
       </c>
     </row>
@@ -4043,22 +4043,22 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>都市频道</t>
+          <t>金色学堂</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>233.18.204.2:5140</t>
+          <t>rtp://233.18.204.14:5140</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/df/都市频道.png</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>金色学堂</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>都市频道</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>https://epg.deny.vip/df/金色学堂.png</t>
         </is>
       </c>
     </row>
@@ -4083,22 +4083,22 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>金色学堂</t>
+          <t>法治天地</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>233.18.204.14:5140</t>
+          <t>rtp://233.18.204.12:5140</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/df/金色学堂.png</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>法治天地</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>金色学堂</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>https://epg.deny.vip/df/法治天地.png</t>
         </is>
       </c>
     </row>
@@ -4123,22 +4123,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>法治天地</t>
+          <t>第一财经</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>233.18.204.12:5140</t>
+          <t>rtp://233.18.204.5:5140</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/df/法治天地.png</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>第一财经</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4148,12 +4148,12 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>法治天地</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>https://epg.deny.vip/df/第一财经.png</t>
         </is>
       </c>
     </row>
@@ -4163,22 +4163,22 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>第一财经</t>
+          <t>游戏风云</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>233.18.204.5:5140</t>
+          <t>rtp://233.18.204.13:5140</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/df/第一财经.png</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>游戏风云</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>第一财经</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>https://epg.deny.vip/df/游戏风云.png</t>
         </is>
       </c>
     </row>
@@ -4203,37 +4203,37 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>游戏风云</t>
+          <t>CCTV-1</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>233.18.204.13:5140</t>
+          <t>rtp://233.18.204.20:5140</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/df/游戏风云.png</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>CCTV-1</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>地方;标清</t>
+          <t>央视;标清</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>游戏风云</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>https://epg.deny.vip/cctv/CCTV-1.png</t>
         </is>
       </c>
     </row>
@@ -4243,22 +4243,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>CCTV-1</t>
+          <t>CCTV-2</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>233.18.204.20:5140</t>
+          <t>rtp://233.18.204.21:5140</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/cctv/CCTV-1.png</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>CCTV-2</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>CCTV-1</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>https://epg.deny.vip/cctv/CCTV-2.png</t>
         </is>
       </c>
     </row>
@@ -4283,22 +4283,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>CCTV-2</t>
+          <t>CCTV-3</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>233.18.204.21:5140</t>
+          <t>rtp://233.18.204.22:5140</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/cctv/CCTV-2.png</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>CCTV-3</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4308,12 +4308,12 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>CCTV-2</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>https://epg.deny.vip/cctv/CCTV-3.png</t>
         </is>
       </c>
     </row>
@@ -4323,22 +4323,22 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>CCTV-3</t>
+          <t>CCTV-4</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>233.18.204.22:5140</t>
+          <t>rtp://233.18.204.23:5140</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/cctv/CCTV-3.png</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>CCTV-4</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4348,12 +4348,12 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>CCTV-3</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>https://epg.deny.vip/cctv/CCTV-4.png</t>
         </is>
       </c>
     </row>
@@ -4363,37 +4363,37 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>CCTV-4</t>
+          <t>CCTV-5</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>233.18.204.23:5140</t>
+          <t>rtp://233.18.204.24:5140</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/cctv/CCTV-4.png</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>CCTV-5</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>央视;标清</t>
+          <t>央视;体育;标清</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>CCTV-4</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>https://epg.deny.vip/cctv/CCTV-5.png</t>
         </is>
       </c>
     </row>
@@ -4403,37 +4403,37 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>CCTV-5</t>
+          <t>CCTV-6</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>233.18.204.24:5140</t>
+          <t>rtp://233.18.204.25:5140</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/cctv/CCTV-5.png</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>CCTV-6</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>央视;体育;标清</t>
+          <t>央视;影视;标清</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>CCTV-5</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>https://epg.deny.vip/cctv/CCTV-6.png</t>
         </is>
       </c>
     </row>
@@ -4443,37 +4443,37 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>CCTV-6</t>
+          <t>CCTV-7</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>233.18.204.25:5140</t>
+          <t>rtp://233.18.204.26:5140</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/cctv/CCTV-6.png</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>CCTV-7</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>央视;影视;标清</t>
+          <t>央视;标清</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>CCTV-6</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>https://epg.deny.vip/cctv/CCTV-7.png</t>
         </is>
       </c>
     </row>
@@ -4483,22 +4483,22 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>CCTV-7</t>
+          <t>CCTV-8</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>233.18.204.26:5140</t>
+          <t>rtp://233.18.204.27:5140</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/cctv/CCTV-7.png</t>
+          <t>19</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>CCTV-8</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4508,12 +4508,12 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>CCTV-7</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>https://epg.deny.vip/cctv/CCTV-8.png</t>
         </is>
       </c>
     </row>
@@ -4523,22 +4523,22 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>CCTV-8</t>
+          <t>CCTV-9</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>233.18.204.27:5140</t>
+          <t>rtp://233.18.204.40:5140</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/cctv/CCTV-8.png</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>CCTV-9</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4548,12 +4548,12 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>CCTV-8</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>https://epg.deny.vip/cctv/CCTV-9.png</t>
         </is>
       </c>
     </row>
@@ -4563,22 +4563,22 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>CCTV-9</t>
+          <t>CCTV-10</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>233.18.204.40:5140</t>
+          <t>rtp://233.18.204.29:5140</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/cctv/CCTV-9.png</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>CCTV-10</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4588,12 +4588,12 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>CCTV-9</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>https://epg.deny.vip/cctv/CCTV-10.png</t>
         </is>
       </c>
     </row>
@@ -4603,22 +4603,22 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>CCTV-10</t>
+          <t>CCTV-11</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>233.18.204.29:5140</t>
+          <t>rtp://233.18.204.30:5140</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/cctv/CCTV-10.png</t>
+          <t>22</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>CCTV-11</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>CCTV-10</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>https://epg.deny.vip/cctv/CCTV-11.png</t>
         </is>
       </c>
     </row>
@@ -4643,22 +4643,22 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>CCTV-11</t>
+          <t>CCTV-12</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>233.18.204.30:5140</t>
+          <t>rtp://233.18.204.31:5140</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/cctv/CCTV-11.png</t>
+          <t>23</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>CCTV-12</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>CCTV-11</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>https://epg.deny.vip/cctv/CCTV-12.png</t>
         </is>
       </c>
     </row>
@@ -4683,22 +4683,22 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>CCTV-12</t>
+          <t>CCTV-13</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>233.18.204.31:5140</t>
+          <t>rtp://233.18.204.32:5140</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/cctv/CCTV-12.png</t>
+          <t>24</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>CCTV-13</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4708,12 +4708,12 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>CCTV-12</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>https://epg.deny.vip/cctv/CCTV-13.png</t>
         </is>
       </c>
     </row>
@@ -4723,22 +4723,22 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>CCTV-13</t>
+          <t>CCTV-14</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>233.18.204.32:5140</t>
+          <t>rtp://233.18.204.33:5140</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/cctv/CCTV-13.png</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>CCTV-14</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>CCTV-13</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>https://epg.deny.vip/cctv/CCTV-14.png</t>
         </is>
       </c>
     </row>
@@ -4763,22 +4763,22 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>CCTV-14</t>
+          <t>CCTV-15</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>233.18.204.33:5140</t>
+          <t>rtp://233.18.204.34:5140</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/cctv/CCTV-14.png</t>
+          <t>26</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>CCTV-15</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>CCTV-14</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>https://epg.deny.vip/cctv/CCTV-15.png</t>
         </is>
       </c>
     </row>
@@ -4803,22 +4803,22 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>CCTV-15</t>
+          <t>CCTV-17</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>233.18.204.34:5140</t>
+          <t>rtp://233.18.204.35:5140</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/cctv/CCTV-15.png</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>CCTV-17</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4828,12 +4828,12 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>CCTV-15</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>https://epg.deny.vip/cctv/CCTV-17.png</t>
         </is>
       </c>
     </row>
@@ -4843,37 +4843,37 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>CCTV-17</t>
+          <t>CETV-1</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>233.18.204.35:5140</t>
+          <t>rtp://233.18.204.153:5140</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/cctv/CCTV-17.png</t>
+          <t>28</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>CETV-1</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>央视;标清</t>
+          <t>标清</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>CCTV-17</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>https://epg.deny.vip/cctv/CETV-1.png</t>
         </is>
       </c>
     </row>
@@ -4883,22 +4883,22 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>CETV-1</t>
+          <t>CETV-2</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>233.18.204.153:5140</t>
+          <t>rtp://233.18.204.154:5140</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/cctv/CETV-1.png</t>
+          <t>29</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>CETV-2</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>CETV-1</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>https://epg.deny.vip/cctv/CETV-2.png</t>
         </is>
       </c>
     </row>
@@ -4923,22 +4923,22 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>CETV-2</t>
+          <t>CGTN</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>233.18.204.154:5140</t>
+          <t>rtp://233.18.204.28:5140</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/cctv/CETV-2.png</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>CGTN</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4948,12 +4948,12 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>CETV-2</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>https://epg.deny.vip/cctv/CGTN.png</t>
         </is>
       </c>
     </row>
@@ -4963,37 +4963,37 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>CGTN</t>
+          <t>安徽卫视</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>233.18.204.28:5140</t>
+          <t>rtp://233.18.204.127:5140</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/cctv/CGTN.png</t>
+          <t>31</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>安徽卫视</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>标清</t>
+          <t>卫视;标清</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>CGTN</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>https://epg.deny.vip/ws/anhui.png</t>
         </is>
       </c>
     </row>
@@ -5003,22 +5003,22 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>安徽卫视</t>
+          <t>北京卫视</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>233.18.204.127:5140</t>
+          <t>rtp://233.18.204.118:5140</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/anhui.png</t>
+          <t>32</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>北京卫视</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -5028,12 +5028,12 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>安徽卫视</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>https://epg.deny.vip/ws/beijing.png</t>
         </is>
       </c>
     </row>
@@ -5048,32 +5048,32 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>233.18.204.118:5140</t>
+          <t>rtp://233.18.204.210:5140</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>北京卫视</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>卫视;标清</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>720x576</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
           <t>https://epg.deny.vip/ws/beijing.png</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>720x576</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>卫视;标清</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>北京卫视</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>32</t>
         </is>
       </c>
     </row>
@@ -5083,22 +5083,22 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>北京卫视</t>
+          <t>兵团卫视</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>233.18.204.210:5140</t>
+          <t>rtp://233.18.204.148:5140</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/beijing.png</t>
+          <t>34</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>兵团卫视</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -5108,12 +5108,12 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>北京卫视</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>https://epg.deny.vip/ws/bingtuan.png</t>
         </is>
       </c>
     </row>
@@ -5123,37 +5123,37 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>兵团卫视</t>
+          <t>财富天下</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>233.18.204.148:5140</t>
+          <t>rtp://233.18.204.41:5140</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/bingtuan.png</t>
+          <t>35</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>财富天下</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>卫视;标清</t>
+          <t>地方;标清</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>兵团卫视</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>https://epg.deny.vip/df/财富天下.png</t>
         </is>
       </c>
     </row>
@@ -5163,37 +5163,37 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>财富天下</t>
+          <t>东南卫视</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>233.18.204.41:5140</t>
+          <t>rtp://233.18.204.128:5140</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/df/财富天下.png</t>
+          <t>36</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>东南卫视</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>地方;标清</t>
+          <t>卫视;标清</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>财富天下</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>https://epg.deny.vip/ws/dongnan.png</t>
         </is>
       </c>
     </row>
@@ -5203,22 +5203,22 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>东南卫视</t>
+          <t>甘肃卫视</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>233.18.204.128:5140</t>
+          <t>rtp://233.18.204.137:5140</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/dongnan.png</t>
+          <t>37</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>甘肃卫视</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -5228,12 +5228,12 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>东南卫视</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>https://epg.deny.vip/ws/gansu.png</t>
         </is>
       </c>
     </row>
@@ -5243,22 +5243,22 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>甘肃卫视</t>
+          <t>广东卫视</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>233.18.204.137:5140</t>
+          <t>rtp://233.18.204.138:5140</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/gansu.png</t>
+          <t>38</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>广东卫视</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>甘肃卫视</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>https://epg.deny.vip/ws/guangdong.png</t>
         </is>
       </c>
     </row>
@@ -5283,22 +5283,22 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>广东卫视</t>
+          <t>广西卫视</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>233.18.204.138:5140</t>
+          <t>rtp://233.18.204.123:5140</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/guangdong.png</t>
+          <t>39</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>广西卫视</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5308,12 +5308,12 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>广东卫视</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>https://epg.deny.vip/ws/guangxi.png</t>
         </is>
       </c>
     </row>
@@ -5323,22 +5323,22 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>广西卫视</t>
+          <t>贵州卫视</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>233.18.204.123:5140</t>
+          <t>rtp://233.18.204.144:5140</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/guangxi.png</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>贵州卫视</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>广西卫视</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>https://epg.deny.vip/ws/guizhou.png</t>
         </is>
       </c>
     </row>
@@ -5363,22 +5363,22 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>贵州卫视</t>
+          <t>海南卫视</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>233.18.204.144:5140</t>
+          <t>rtp://233.18.204.122:5140</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/guizhou.png</t>
+          <t>41</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>海南卫视</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5388,12 +5388,12 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>贵州卫视</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>https://epg.deny.vip/ws/hainan.png</t>
         </is>
       </c>
     </row>
@@ -5403,22 +5403,22 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>海南卫视</t>
+          <t>河北卫视</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>233.18.204.122:5140</t>
+          <t>rtp://233.18.204.140:5140</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/hainan.png</t>
+          <t>42</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>河北卫视</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5428,12 +5428,12 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>海南卫视</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>https://epg.deny.vip/ws/hebei.png</t>
         </is>
       </c>
     </row>
@@ -5443,22 +5443,22 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>河北卫视</t>
+          <t>河南卫视</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>233.18.204.140:5140</t>
+          <t>rtp://233.18.204.145:5140</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/hebei.png</t>
+          <t>43</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>河南卫视</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5468,12 +5468,12 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>河北卫视</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>https://epg.deny.vip/ws/henan.png</t>
         </is>
       </c>
     </row>
@@ -5483,22 +5483,22 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>河南卫视</t>
+          <t>黑龙江卫视</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>233.18.204.145:5140</t>
+          <t>rtp://233.18.204.139:5140</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/henan.png</t>
+          <t>44</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>黑龙江卫视</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5508,12 +5508,12 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>河南卫视</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>https://epg.deny.vip/ws/heilongjiang.png</t>
         </is>
       </c>
     </row>
@@ -5523,22 +5523,22 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>黑龙江卫视</t>
+          <t>湖北卫视</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>233.18.204.139:5140</t>
+          <t>rtp://233.18.204.142:5140</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/heilongjiang.png</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>湖北卫视</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5548,12 +5548,12 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>黑龙江卫视</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>https://epg.deny.vip/ws/hubei.png</t>
         </is>
       </c>
     </row>
@@ -5563,22 +5563,22 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>湖北卫视</t>
+          <t>湖南卫视</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>233.18.204.142:5140</t>
+          <t>rtp://233.18.204.119:5140</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/hubei.png</t>
+          <t>46</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>湖南卫视</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>湖北卫视</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>https://epg.deny.vip/ws/hunan.png</t>
         </is>
       </c>
     </row>
@@ -5603,22 +5603,22 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>湖南卫视</t>
+          <t>吉林卫视</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>233.18.204.119:5140</t>
+          <t>rtp://233.18.204.131:5140</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/hunan.png</t>
+          <t>47</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>吉林卫视</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5628,12 +5628,12 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>湖南卫视</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>https://epg.deny.vip/ws/jilin.png</t>
         </is>
       </c>
     </row>
@@ -5643,37 +5643,37 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>吉林卫视</t>
+          <t>家庭理财</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>233.18.204.131:5140</t>
+          <t>rtp://233.18.204.157:5140</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/jilin.png</t>
+          <t>48</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>家庭理财</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>卫视;标清</t>
+          <t>标清</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>吉林卫视</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>https://epg.deny.vip/df/家庭理财.png</t>
         </is>
       </c>
     </row>
@@ -5683,37 +5683,37 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>家庭理财</t>
+          <t>嘉佳卡通</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>233.18.204.157:5140</t>
+          <t>rtp://233.18.204.151:5140</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/df/家庭理财.png</t>
+          <t>49</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>嘉佳卡通</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>标清</t>
+          <t>标清;卡通</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>家庭理财</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>https://epg.deny.vip/df/嘉佳卡通.png</t>
         </is>
       </c>
     </row>
@@ -5723,37 +5723,37 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>嘉佳卡通</t>
+          <t>江苏卫视</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>233.18.204.151:5140</t>
+          <t>rtp://233.18.204.120:5140</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/df/嘉佳卡通.png</t>
+          <t>50</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>江苏卫视</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>标清;卡通</t>
+          <t>卫视;标清</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>嘉佳卡通</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>https://epg.deny.vip/ws/jiangsu.png</t>
         </is>
       </c>
     </row>
@@ -5763,22 +5763,22 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>江苏卫视</t>
+          <t>江西卫视</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>233.18.204.120:5140</t>
+          <t>rtp://233.18.204.130:5140</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/jiangsu.png</t>
+          <t>51</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>江西卫视</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>江苏卫视</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>https://epg.deny.vip/ws/jiangxi.png</t>
         </is>
       </c>
     </row>
@@ -5803,22 +5803,22 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>江西卫视</t>
+          <t>云南卫视</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>233.18.204.130:5140</t>
+          <t>rtp://233.18.204.136:5140</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/jiangxi.png</t>
+          <t>52</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>云南卫视</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>江西卫视</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>https://epg.deny.vip/ws/yunnan.png</t>
         </is>
       </c>
     </row>
@@ -5843,37 +5843,37 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>云南卫视</t>
+          <t>金鹰卡通</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>233.18.204.136:5140</t>
+          <t>rtp://233.18.204.150:5140</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/yunnan.png</t>
+          <t>53</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>金鹰卡通</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>卫视;标清</t>
+          <t>卫视;标清;卡通</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>云南卫视</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>https://epg.deny.vip/df/金鹰卡通.png</t>
         </is>
       </c>
     </row>
@@ -5883,22 +5883,22 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>金鹰卡通</t>
+          <t>卡酷少儿</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>233.18.204.150:5140</t>
+          <t>rtp://233.18.204.152:5140</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/df/金鹰卡通.png</t>
+          <t>54</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>卡酷少儿</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5908,12 +5908,12 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>金鹰卡通</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>https://epg.deny.vip/df/卡酷少儿.png</t>
         </is>
       </c>
     </row>
@@ -5923,37 +5923,37 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>卡酷少儿</t>
+          <t>辽宁卫视</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>233.18.204.152:5140</t>
+          <t>rtp://233.18.204.126:5140</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/df/卡酷少儿.png</t>
+          <t>55</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>辽宁卫视</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>卫视;标清;卡通</t>
+          <t>卫视;标清</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>卡酷少儿</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>https://epg.deny.vip/ws/liaoning.png</t>
         </is>
       </c>
     </row>
@@ -5963,22 +5963,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>辽宁卫视</t>
+          <t>内蒙古卫视</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>233.18.204.126:5140</t>
+          <t>rtp://233.18.204.141:5140</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/liaoning.png</t>
+          <t>56</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>内蒙古卫视</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>辽宁卫视</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>https://epg.deny.vip/ws/neimeng.png</t>
         </is>
       </c>
     </row>
@@ -6003,22 +6003,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>内蒙古卫视</t>
+          <t>宁夏卫视</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>233.18.204.141:5140</t>
+          <t>rtp://233.18.204.117:5140</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/neimeng.png</t>
+          <t>57</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>宁夏卫视</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -6028,12 +6028,12 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>内蒙古卫视</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>https://epg.deny.vip/ws/ningxia.png</t>
         </is>
       </c>
     </row>
@@ -6043,22 +6043,22 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>宁夏卫视</t>
+          <t>青海卫视</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>233.18.204.117:5140</t>
+          <t>rtp://233.18.204.133:5140</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/ningxia.png</t>
+          <t>58</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>青海卫视</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>宁夏卫视</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>https://epg.deny.vip/ws/qinghai.png</t>
         </is>
       </c>
     </row>
@@ -6083,22 +6083,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>青海卫视</t>
+          <t>三沙卫视</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>233.18.204.133:5140</t>
+          <t>rtp://233.18.204.149:5140</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/qinghai.png</t>
+          <t>59</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>三沙卫视</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -6108,12 +6108,12 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>青海卫视</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>https://epg.deny.vip/ws/sansha.png</t>
         </is>
       </c>
     </row>
@@ -6123,22 +6123,22 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>三沙卫视</t>
+          <t>山东卫视</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>233.18.204.149:5140</t>
+          <t>rtp://233.18.204.125:5140</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/sansha.png</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>山东卫视</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>三沙卫视</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>https://epg.deny.vip/ws/shandong.png</t>
         </is>
       </c>
     </row>
@@ -6163,22 +6163,22 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>山东卫视</t>
+          <t>山西卫视</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>233.18.204.125:5140</t>
+          <t>rtp://233.18.204.132:5140</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/shandong.png</t>
+          <t>61</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>山西卫视</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -6188,12 +6188,12 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>山东卫视</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>https://epg.deny.vip/ws/shanxi_.png</t>
         </is>
       </c>
     </row>
@@ -6203,22 +6203,22 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>山西卫视</t>
+          <t>陕西卫视</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>233.18.204.132:5140</t>
+          <t>rtp://233.18.204.135:5140</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/shanxi_.png</t>
+          <t>62</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>陕西卫视</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>山西卫视</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>https://epg.deny.vip/ws/shanxi.png</t>
         </is>
       </c>
     </row>
@@ -6243,22 +6243,22 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>陕西卫视</t>
+          <t>深圳卫视</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>233.18.204.135:5140</t>
+          <t>rtp://233.18.204.146:5140</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/shanxi.png</t>
+          <t>63</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>深圳卫视</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -6268,12 +6268,12 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>陕西卫视</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>https://epg.deny.vip/ws/shenzhen.png</t>
         </is>
       </c>
     </row>
@@ -6283,22 +6283,22 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>深圳卫视</t>
+          <t>四川卫视</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>233.18.204.146:5140</t>
+          <t>rtp://233.18.204.124:5140</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/shenzhen.png</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>四川卫视</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>深圳卫视</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>https://epg.deny.vip/ws/sichuan.png</t>
         </is>
       </c>
     </row>
@@ -6323,22 +6323,22 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>四川卫视</t>
+          <t>天津卫视</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>233.18.204.124:5140</t>
+          <t>rtp://233.18.204.129:5140</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/sichuan.png</t>
+          <t>65</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>天津卫视</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -6348,12 +6348,12 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>四川卫视</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>https://epg.deny.vip/ws/tianjin.png</t>
         </is>
       </c>
     </row>
@@ -6363,22 +6363,22 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>天津卫视</t>
+          <t>西藏卫视</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>233.18.204.129:5140</t>
+          <t>rtp://233.18.204.134:5140</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/tianjin.png</t>
+          <t>66</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>西藏卫视</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -6388,12 +6388,12 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>天津卫视</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>https://epg.deny.vip/ws/xizang.png</t>
         </is>
       </c>
     </row>
@@ -6403,22 +6403,22 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>西藏卫视</t>
+          <t>新疆卫视</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>233.18.204.134:5140</t>
+          <t>rtp://233.18.204.147:5140</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/xizang.png</t>
+          <t>67</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>新疆卫视</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6428,12 +6428,12 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>西藏卫视</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>https://epg.deny.vip/ws/xinjiang.png</t>
         </is>
       </c>
     </row>
@@ -6443,22 +6443,22 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>新疆卫视</t>
+          <t>延边卫视</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>233.18.204.147:5140</t>
+          <t>rtp://233.18.204.155:5140</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/xinjiang.png</t>
+          <t>68</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>延边卫视</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6468,12 +6468,12 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>新疆卫视</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>https://epg.deny.vip/ws/yanbian.png</t>
         </is>
       </c>
     </row>
@@ -6483,22 +6483,22 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>延边卫视</t>
+          <t>浙江卫视</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>233.18.204.155:5140</t>
+          <t>rtp://233.18.204.121:5140</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/yanbian.png</t>
+          <t>69</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>浙江卫视</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>延边卫视</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>https://epg.deny.vip/ws/zhejiang.png</t>
         </is>
       </c>
     </row>
@@ -6523,22 +6523,22 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>浙江卫视</t>
+          <t>重庆卫视</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>233.18.204.121:5140</t>
+          <t>rtp://233.18.204.143:5140</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/zhejiang.png</t>
+          <t>70</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>重庆卫视</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>浙江卫视</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>https://epg.deny.vip/ws/chongqing.png</t>
         </is>
       </c>
     </row>
@@ -6563,37 +6563,37 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>重庆卫视</t>
+          <t>央广购物</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>233.18.204.143:5140</t>
+          <t>rtp://233.18.204.39:5140</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/chongqing.png</t>
+          <t>71</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>央广购物</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>卫视;标清</t>
+          <t>央视;标清</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>重庆卫视</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>#&lt;MISSING&gt;</t>
         </is>
       </c>
     </row>
@@ -6608,17 +6608,17 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>233.18.204.39:5140</t>
+          <t>rtp://233.18.204.15:5140</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t/>
+          <t>72</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>央广购物</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -6628,12 +6628,12 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>央广购物</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>#&lt;MISSING&gt;</t>
         </is>
       </c>
     </row>
@@ -6643,37 +6643,37 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>央广购物</t>
+          <t>东方购物</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>233.18.204.15:5140</t>
+          <t>rtp://233.18.204.9:5140</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t/>
+          <t>73</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>东方购物</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>央视;标清</t>
+          <t>地方;标清</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>央广购物</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>#&lt;MISSING&gt;</t>
         </is>
       </c>
     </row>
@@ -6683,22 +6683,22 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>东方购物</t>
+          <t>东方购物-1</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>233.18.204.9:5140</t>
+          <t>rtp://233.18.204.10:5140</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t/>
+          <t>74</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>东方购物-1</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6708,12 +6708,12 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>东方购物</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>#&lt;MISSING&gt;</t>
         </is>
       </c>
     </row>
@@ -6723,37 +6723,37 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>东方购物-1</t>
+          <t>好享购物</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>233.18.204.10:5140</t>
+          <t>rtp://233.18.204.36:5140</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t/>
+          <t>75</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>好享购物</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>地方;标清</t>
+          <t>标清</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>东方购物-1</t>
+          <t>720x576</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>#&lt;MISSING&gt;</t>
         </is>
       </c>
     </row>
@@ -6763,37 +6763,37 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>好享购物</t>
+          <t>东方卫视4K</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>233.18.204.36:5140</t>
+          <t>rtp://233.18.204.224:5140</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t/>
+          <t>303</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>720x576</t>
+          <t>东方卫视</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>标清</t>
+          <t>卫视;高清;4K</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>好享购物</t>
+          <t>3840x2160</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>https://epg.deny.vip/ws/dongfang.png</t>
         </is>
       </c>
     </row>
@@ -6803,37 +6803,37 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>东方卫视4K</t>
+          <t>欢笑剧场 4K</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>233.18.204.224:5140</t>
+          <t>rtp://233.18.204.205:5140</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/dongfang.png</t>
+          <t>304</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
+          <t>欢笑剧场</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>地方;高清;4K;高码</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
           <t>3840x2160</t>
         </is>
       </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>卫视;高清;4K</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>东方卫视</t>
-        </is>
-      </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>https://epg.deny.vip/df/欢笑剧场4K.png</t>
         </is>
       </c>
     </row>
@@ -6848,32 +6848,32 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>233.18.204.205:5140</t>
+          <t>rtp://233.18.204.50:5140</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>欢笑剧场</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>地方;高清;4K;高码</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>3840x2160</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
           <t>https://epg.deny.vip/df/欢笑剧场4K.png</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>3840x2160</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>地方;高清;4K;高码</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>欢笑剧场</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>304</t>
         </is>
       </c>
     </row>
@@ -6883,37 +6883,37 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>欢笑剧场 4K</t>
+          <t>欢笑剧场 4K 普通4K</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>233.18.204.50:5140</t>
+          <t>rtp://233.18.204.115:5140</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>欢笑剧场</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>地方;高清;4K</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>3840x2160</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
           <t>https://epg.deny.vip/df/欢笑剧场4K.png</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>3840x2160</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>地方;高清;4K;高码</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>欢笑剧场</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>305</t>
         </is>
       </c>
     </row>
@@ -6923,37 +6923,37 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>欢笑剧场 4K 普通4K</t>
+          <t>CCTV 4K</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>233.18.204.115:5140</t>
+          <t>rtp://233.18.204.204:5140</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/df/欢笑剧场4K.png</t>
+          <t>307</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
+          <t>CCTV 4K</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>央视;高清;4K;高码</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
           <t>3840x2160</t>
         </is>
       </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>地方;高清;4K</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>欢笑剧场</t>
-        </is>
-      </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>https://epg.deny.vip/cctv/CCTV-4K.png</t>
         </is>
       </c>
     </row>
@@ -6963,37 +6963,37 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
+          <t>CCTV 4K 普通4K</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>rtp://233.18.204.188:5140</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
           <t>CCTV 4K</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>233.18.204.204:5140</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>央视;高清;4K</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>3840x2160</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
         <is>
           <t>https://epg.deny.vip/cctv/CCTV-4K.png</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>3840x2160</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>央视;高清;4K;高码</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>CCTV 4K</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>307</t>
         </is>
       </c>
     </row>
@@ -7003,37 +7003,37 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>CCTV 4K 普通4K</t>
+          <t>CCTV-16 4K</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>233.18.204.188:5140</t>
+          <t>rtp://233.18.204.215:5140</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/cctv/CCTV-4K.png</t>
+          <t>309</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
+          <t>CCTV-16</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>央视;体育;4K;高码</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
           <t>3840x2160</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>央视;高清;4K</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>CCTV 4K</t>
-        </is>
-      </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>https://epg.deny.vip/cctv/CCTV-16.png</t>
         </is>
       </c>
     </row>
@@ -7043,37 +7043,37 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>CCTV-16 4K</t>
+          <t>CCTV-16 普通4K</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>233.18.204.215:5140</t>
+          <t>rtp://233.18.204.114:5140</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>CCTV-16</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>央视;体育;高清;4K</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>3840x2160</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
           <t>https://epg.deny.vip/cctv/CCTV-16.png</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>3840x2160</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>央视;体育;4K;高码</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>CCTV-16</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>309</t>
         </is>
       </c>
     </row>
@@ -7083,37 +7083,37 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>CCTV-16 普通4K</t>
+          <t>北京卫视 4K</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>233.18.204.114:5140</t>
+          <t>rtp://233.18.204.209:5140</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/cctv/CCTV-16.png</t>
+          <t>311</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
+          <t>北京卫视</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>卫视;高清;4K</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
           <t>3840x2160</t>
         </is>
       </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>央视;体育;高清;4K</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>CCTV-16</t>
-        </is>
-      </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>https://epg.deny.vip/ws/beijing.png</t>
         </is>
       </c>
     </row>
@@ -7123,37 +7123,37 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>北京卫视 4K</t>
+          <t>广东卫视 4K</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>233.18.204.209:5140</t>
+          <t>rtp://233.18.204.218:5140</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/beijing.png</t>
+          <t>312</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
+          <t>广东卫视</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>卫视;高清;4K</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
           <t>3840x2160</t>
         </is>
       </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>卫视;高清;4K</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>北京卫视</t>
-        </is>
-      </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>https://epg.deny.vip/ws/guangdong.png</t>
         </is>
       </c>
     </row>
@@ -7163,37 +7163,37 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>广东卫视 4K</t>
+          <t>江苏卫视4K</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>233.18.204.218:5140</t>
+          <t>rtp://233.18.204.226:5140</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/guangdong.png</t>
+          <t>313</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
+          <t>江苏卫视</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>卫视;高清;4K</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
           <t>3840x2160</t>
         </is>
       </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>卫视;高清;4K</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>广东卫视</t>
-        </is>
-      </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>https://epg.deny.vip/ws/jiangsu.png</t>
         </is>
       </c>
     </row>
@@ -7203,37 +7203,37 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>江苏卫视4K</t>
+          <t>山东卫视4K</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>233.18.204.226:5140</t>
+          <t>rtp://233.18.204.228:5140</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/jiangsu.png</t>
+          <t>314</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
+          <t>山东卫视</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>卫视;高清;4K</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
           <t>3840x2160</t>
         </is>
       </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>卫视;高清;4K</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>江苏卫视</t>
-        </is>
-      </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>https://epg.deny.vip/ws/shandong.png</t>
         </is>
       </c>
     </row>
@@ -7243,37 +7243,37 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>山东卫视4K</t>
+          <t>深圳卫视 4K</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>233.18.204.228:5140</t>
+          <t>rtp://233.18.204.219:5140</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/shandong.png</t>
+          <t>315</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
+          <t>深圳卫视</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>卫视;高清;4K</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
           <t>3840x2160</t>
         </is>
       </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>卫视;高清;4K</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>山东卫视</t>
-        </is>
-      </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>https://epg.deny.vip/ws/shenzhen.png</t>
         </is>
       </c>
     </row>
@@ -7283,37 +7283,37 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>深圳卫视 4K</t>
+          <t>四川卫视4K</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>233.18.204.219:5140</t>
+          <t>rtp://233.18.204.225:5140</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/shenzhen.png</t>
+          <t>316</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
+          <t>四川卫视</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>卫视;高清;4K</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
           <t>3840x2160</t>
         </is>
       </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>卫视;高清;4K</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>深圳卫视</t>
-        </is>
-      </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>https://epg.deny.vip/ws/sichuan.png</t>
         </is>
       </c>
     </row>
@@ -7323,77 +7323,37 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>四川卫视4K</t>
+          <t>天翼高清宣传片</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>233.18.204.225:5140</t>
+          <t>rtp://233.18.204.201:5140</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>https://epg.deny.vip/ws/sichuan.png</t>
+          <t>317</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
+          <t>天翼高清宣传片</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>测试;4K</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
           <t>3840x2160</t>
         </is>
       </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>卫视;高清;4K</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>四川卫视</t>
-        </is>
-      </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>316</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="n">
-        <v>-1</v>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>天翼高清宣传片</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>233.18.204.201:5140</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>3840x2160</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>测试;4K</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>天翼高清宣传片</t>
-        </is>
-      </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>317</t>
+          <t>#&lt;MISSING&gt;</t>
         </is>
       </c>
     </row>
